--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Columbus-Daylighting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C640141C-78D8-452D-8020-E959B7A733E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F380CA6D-46CE-459A-AFD6-56DF2CC3ECA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -823,7 +823,7 @@
         <v>46176.47314814815</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" t="s">
         <v>11</v>
@@ -852,7 +852,7 @@
         <v>46176.47384259259</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" t="s">
         <v>11</v>
@@ -910,7 +910,7 @@
         <v>46176.460763888892</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Columbus-Daylighting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E69FFF5-D02D-4BCE-8F36-8713B8A1B0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{872FF147-0BAB-450A-BFAC-1BE117F4EAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -484,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -3092,6 +3092,7 @@
     <row r="378" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H378" s="2"/>
       <c r="I378" s="1"/>
+      <c r="J378" s="2"/>
       <c r="K378" s="1"/>
     </row>
     <row r="379" spans="8:11" x14ac:dyDescent="0.3">
@@ -39158,7 +39159,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Columbus-Daylighting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{872FF147-0BAB-450A-BFAC-1BE117F4EAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD3D7D6F-F7CC-41D9-9B4B-19E73E631F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="25">
   <si>
     <t>Company Name</t>
   </si>
@@ -83,13 +83,16 @@
     <t>PENDING</t>
   </si>
   <si>
+    <t>Mark Complete</t>
+  </si>
+  <si>
     <t>Rules for Safe Driving</t>
   </si>
   <si>
-    <t>Drowsy Driving</t>
+    <t>Driver Health</t>
   </si>
   <si>
-    <t>Mark Complete</t>
+    <t>Drowsy Driving</t>
   </si>
   <si>
     <t>Space Management for Commercial Vehicles</t>
@@ -484,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -533,16 +536,16 @@
     </row>
     <row r="2" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2">
         <v>5263</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>12</v>
@@ -566,21 +569,21 @@
       <c r="J3" s="2"/>
       <c r="K3" s="1"/>
       <c r="M3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4">
         <v>5264</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>13</v>
@@ -600,16 +603,16 @@
     </row>
     <row r="5" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5">
         <v>5262</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>13</v>
@@ -629,16 +632,16 @@
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6">
         <v>5263</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>13</v>
@@ -658,16 +661,16 @@
     </row>
     <row r="7" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7">
         <v>5264</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>13</v>
@@ -687,16 +690,16 @@
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8">
         <v>5262</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>13</v>
@@ -716,16 +719,16 @@
     </row>
     <row r="9" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9">
         <v>5263</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>13</v>
@@ -745,16 +748,16 @@
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E10">
         <v>5264</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>13</v>
@@ -774,16 +777,16 @@
     </row>
     <row r="11" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11">
         <v>5262</v>
       </c>
       <c r="F11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>13</v>
@@ -803,16 +806,16 @@
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E12">
         <v>5263</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>13</v>
@@ -832,16 +835,16 @@
     </row>
     <row r="13" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E13">
         <v>5264</v>
       </c>
       <c r="F13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>13</v>
@@ -861,16 +864,16 @@
     </row>
     <row r="14" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E14">
         <v>5615</v>
       </c>
       <c r="F14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>10</v>
@@ -890,16 +893,16 @@
     </row>
     <row r="15" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E15">
         <v>5262</v>
       </c>
       <c r="F15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>13</v>
@@ -918,102 +921,194 @@
       </c>
     </row>
     <row r="16" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H16" s="2"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H17" s="2"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="18" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H18" s="2"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="1"/>
-    </row>
-    <row r="19" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H19" s="2"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="1"/>
-    </row>
-    <row r="20" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16">
+        <v>5263</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>46219.678472222222</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17">
+        <v>5264</v>
+      </c>
+      <c r="F17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>46219.678472222222</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18">
+        <v>5615</v>
+      </c>
+      <c r="F18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J18" s="2">
+        <v>9.0393518518518522E-3</v>
+      </c>
+      <c r="K18" s="1">
+        <v>46219.679166666669</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19">
+        <v>5262</v>
+      </c>
+      <c r="F19" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>46219.679861111108</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H20" s="2"/>
       <c r="I20" s="1"/>
       <c r="J20" s="2"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H21" s="2"/>
       <c r="I21" s="1"/>
       <c r="J21" s="2"/>
       <c r="K21" s="1"/>
     </row>
-    <row r="22" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H22" s="2"/>
       <c r="I22" s="1"/>
       <c r="J22" s="2"/>
       <c r="K22" s="1"/>
     </row>
-    <row r="23" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H23" s="2"/>
       <c r="I23" s="1"/>
       <c r="J23" s="2"/>
       <c r="K23" s="1"/>
     </row>
-    <row r="24" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H24" s="2"/>
       <c r="I24" s="1"/>
       <c r="J24" s="2"/>
       <c r="K24" s="1"/>
     </row>
-    <row r="25" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H25" s="2"/>
       <c r="I25" s="1"/>
       <c r="J25" s="2"/>
       <c r="K25" s="1"/>
     </row>
-    <row r="26" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H26" s="2"/>
       <c r="I26" s="1"/>
       <c r="J26" s="2"/>
       <c r="K26" s="1"/>
     </row>
-    <row r="27" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H27" s="2"/>
       <c r="I27" s="1"/>
       <c r="J27" s="2"/>
       <c r="K27" s="1"/>
     </row>
-    <row r="28" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H28" s="2"/>
       <c r="I28" s="1"/>
       <c r="J28" s="2"/>
       <c r="K28" s="1"/>
     </row>
-    <row r="29" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H29" s="2"/>
       <c r="I29" s="1"/>
       <c r="J29" s="2"/>
       <c r="K29" s="1"/>
     </row>
-    <row r="30" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H30" s="2"/>
       <c r="I30" s="1"/>
       <c r="J30" s="2"/>
       <c r="K30" s="1"/>
     </row>
-    <row r="31" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H31" s="2"/>
       <c r="I31" s="1"/>
       <c r="J31" s="2"/>
       <c r="K31" s="1"/>
     </row>
-    <row r="32" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H32" s="2"/>
       <c r="I32" s="1"/>
       <c r="J32" s="2"/>
@@ -3656,6 +3751,7 @@
     <row r="472" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H472" s="2"/>
       <c r="I472" s="1"/>
+      <c r="J472" s="2"/>
       <c r="K472" s="1"/>
     </row>
     <row r="473" spans="8:11" x14ac:dyDescent="0.3">
@@ -5004,6 +5100,7 @@
     <row r="697" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H697" s="2"/>
       <c r="I697" s="1"/>
+      <c r="J697" s="2"/>
       <c r="K697" s="1"/>
     </row>
     <row r="698" spans="8:11" x14ac:dyDescent="0.3">
@@ -5313,6 +5410,7 @@
     <row r="749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H749" s="2"/>
       <c r="I749" s="1"/>
+      <c r="J749" s="2"/>
       <c r="K749" s="1"/>
     </row>
     <row r="750" spans="8:11" x14ac:dyDescent="0.3">
@@ -5402,6 +5500,7 @@
     <row r="764" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H764" s="2"/>
       <c r="I764" s="1"/>
+      <c r="J764" s="2"/>
       <c r="K764" s="1"/>
     </row>
     <row r="765" spans="8:11" x14ac:dyDescent="0.3">
@@ -5508,6 +5607,7 @@
     </row>
     <row r="782" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I782" s="1"/>
+      <c r="J782" s="2"/>
       <c r="K782" s="1"/>
     </row>
     <row r="783" spans="8:11" x14ac:dyDescent="0.3">
@@ -5525,6 +5625,7 @@
     <row r="785" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H785" s="2"/>
       <c r="I785" s="1"/>
+      <c r="J785" s="2"/>
       <c r="K785" s="1"/>
     </row>
     <row r="786" spans="8:11" x14ac:dyDescent="0.3">
@@ -5536,6 +5637,7 @@
     <row r="787" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H787" s="2"/>
       <c r="I787" s="1"/>
+      <c r="J787" s="2"/>
       <c r="K787" s="1"/>
     </row>
     <row r="788" spans="8:11" x14ac:dyDescent="0.3">
@@ -5577,6 +5679,7 @@
     <row r="794" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H794" s="2"/>
       <c r="I794" s="1"/>
+      <c r="J794" s="2"/>
       <c r="K794" s="1"/>
     </row>
     <row r="795" spans="8:11" x14ac:dyDescent="0.3">
@@ -5600,6 +5703,7 @@
     <row r="798" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H798" s="2"/>
       <c r="I798" s="1"/>
+      <c r="J798" s="2"/>
       <c r="K798" s="1"/>
     </row>
     <row r="799" spans="8:11" x14ac:dyDescent="0.3">
@@ -5623,6 +5727,7 @@
     <row r="802" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H802" s="2"/>
       <c r="I802" s="1"/>
+      <c r="J802" s="2"/>
       <c r="K802" s="1"/>
     </row>
     <row r="803" spans="8:11" x14ac:dyDescent="0.3">
@@ -5640,6 +5745,7 @@
     <row r="805" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H805" s="2"/>
       <c r="I805" s="1"/>
+      <c r="J805" s="2"/>
       <c r="K805" s="1"/>
     </row>
     <row r="806" spans="8:11" x14ac:dyDescent="0.3">
@@ -5651,11 +5757,13 @@
     <row r="807" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H807" s="2"/>
       <c r="I807" s="1"/>
+      <c r="J807" s="2"/>
       <c r="K807" s="1"/>
     </row>
     <row r="808" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H808" s="2"/>
       <c r="I808" s="1"/>
+      <c r="J808" s="2"/>
       <c r="K808" s="1"/>
     </row>
     <row r="809" spans="8:11" x14ac:dyDescent="0.3">
@@ -5775,6 +5883,7 @@
     <row r="828" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H828" s="2"/>
       <c r="I828" s="1"/>
+      <c r="J828" s="2"/>
       <c r="K828" s="1"/>
     </row>
     <row r="829" spans="8:11" x14ac:dyDescent="0.3">
@@ -5858,6 +5967,7 @@
     <row r="842" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H842" s="2"/>
       <c r="I842" s="1"/>
+      <c r="J842" s="2"/>
       <c r="K842" s="1"/>
     </row>
     <row r="843" spans="8:11" x14ac:dyDescent="0.3">
@@ -5881,6 +5991,7 @@
     <row r="846" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H846" s="2"/>
       <c r="I846" s="1"/>
+      <c r="J846" s="2"/>
       <c r="K846" s="1"/>
     </row>
     <row r="847" spans="8:11" x14ac:dyDescent="0.3">
@@ -5892,6 +6003,7 @@
     <row r="848" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H848" s="2"/>
       <c r="I848" s="1"/>
+      <c r="J848" s="2"/>
       <c r="K848" s="1"/>
     </row>
     <row r="849" spans="8:11" x14ac:dyDescent="0.3">
@@ -5903,6 +6015,7 @@
     <row r="850" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H850" s="2"/>
       <c r="I850" s="1"/>
+      <c r="J850" s="2"/>
       <c r="K850" s="1"/>
     </row>
     <row r="851" spans="8:11" x14ac:dyDescent="0.3">
@@ -5950,6 +6063,7 @@
     <row r="858" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H858" s="2"/>
       <c r="I858" s="1"/>
+      <c r="J858" s="2"/>
       <c r="K858" s="1"/>
     </row>
     <row r="859" spans="8:11" x14ac:dyDescent="0.3">
@@ -6003,6 +6117,7 @@
     <row r="867" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H867" s="2"/>
       <c r="I867" s="1"/>
+      <c r="J867" s="2"/>
       <c r="K867" s="1"/>
     </row>
     <row r="868" spans="8:11" x14ac:dyDescent="0.3">
@@ -6175,6 +6290,7 @@
     <row r="896" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H896" s="2"/>
       <c r="I896" s="1"/>
+      <c r="J896" s="2"/>
       <c r="K896" s="1"/>
     </row>
     <row r="897" spans="8:11" x14ac:dyDescent="0.3">
@@ -6186,6 +6302,7 @@
     <row r="898" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H898" s="2"/>
       <c r="I898" s="1"/>
+      <c r="J898" s="2"/>
       <c r="K898" s="1"/>
     </row>
     <row r="899" spans="8:11" x14ac:dyDescent="0.3">
@@ -6263,6 +6380,7 @@
     <row r="911" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H911" s="2"/>
       <c r="I911" s="1"/>
+      <c r="J911" s="2"/>
       <c r="K911" s="1"/>
     </row>
     <row r="912" spans="8:11" x14ac:dyDescent="0.3">
@@ -6280,6 +6398,7 @@
     <row r="914" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H914" s="2"/>
       <c r="I914" s="1"/>
+      <c r="J914" s="2"/>
       <c r="K914" s="1"/>
     </row>
     <row r="915" spans="8:11" x14ac:dyDescent="0.3">
@@ -6327,6 +6446,7 @@
     <row r="922" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H922" s="2"/>
       <c r="I922" s="1"/>
+      <c r="J922" s="2"/>
       <c r="K922" s="1"/>
     </row>
     <row r="923" spans="8:11" x14ac:dyDescent="0.3">
@@ -6439,6 +6559,7 @@
     <row r="941" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H941" s="2"/>
       <c r="I941" s="1"/>
+      <c r="J941" s="2"/>
       <c r="K941" s="1"/>
     </row>
     <row r="942" spans="8:11" x14ac:dyDescent="0.3">
@@ -6498,6 +6619,7 @@
     <row r="951" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H951" s="2"/>
       <c r="I951" s="1"/>
+      <c r="J951" s="2"/>
       <c r="K951" s="1"/>
     </row>
     <row r="952" spans="8:11" x14ac:dyDescent="0.3">
@@ -6509,6 +6631,7 @@
     <row r="953" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H953" s="2"/>
       <c r="I953" s="1"/>
+      <c r="J953" s="2"/>
       <c r="K953" s="1"/>
     </row>
     <row r="954" spans="8:11" x14ac:dyDescent="0.3">
@@ -6580,6 +6703,7 @@
     <row r="965" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H965" s="2"/>
       <c r="I965" s="1"/>
+      <c r="J965" s="2"/>
       <c r="K965" s="1"/>
     </row>
     <row r="966" spans="8:11" x14ac:dyDescent="0.3">
@@ -6632,6 +6756,7 @@
     </row>
     <row r="974" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I974" s="1"/>
+      <c r="J974" s="2"/>
       <c r="K974" s="1"/>
     </row>
     <row r="975" spans="8:11" x14ac:dyDescent="0.3">
@@ -6708,11 +6833,13 @@
     <row r="987" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H987" s="2"/>
       <c r="I987" s="1"/>
+      <c r="J987" s="2"/>
       <c r="K987" s="1"/>
     </row>
     <row r="988" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H988" s="2"/>
       <c r="I988" s="1"/>
+      <c r="J988" s="2"/>
       <c r="K988" s="1"/>
     </row>
     <row r="989" spans="8:11" x14ac:dyDescent="0.3">
@@ -6772,6 +6899,7 @@
     <row r="998" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H998" s="2"/>
       <c r="I998" s="1"/>
+      <c r="J998" s="2"/>
       <c r="K998" s="1"/>
     </row>
     <row r="999" spans="8:11" x14ac:dyDescent="0.3">
@@ -6783,6 +6911,7 @@
     <row r="1000" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1000" s="2"/>
       <c r="I1000" s="1"/>
+      <c r="J1000" s="2"/>
       <c r="K1000" s="1"/>
     </row>
     <row r="1001" spans="8:11" x14ac:dyDescent="0.3">
@@ -6794,11 +6923,13 @@
     <row r="1002" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1002" s="2"/>
       <c r="I1002" s="1"/>
+      <c r="J1002" s="2"/>
       <c r="K1002" s="1"/>
     </row>
     <row r="1003" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1003" s="2"/>
       <c r="I1003" s="1"/>
+      <c r="J1003" s="2"/>
       <c r="K1003" s="1"/>
     </row>
     <row r="1004" spans="8:11" x14ac:dyDescent="0.3">
@@ -6852,6 +6983,7 @@
     <row r="1012" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1012" s="2"/>
       <c r="I1012" s="1"/>
+      <c r="J1012" s="2"/>
       <c r="K1012" s="1"/>
     </row>
     <row r="1013" spans="8:11" x14ac:dyDescent="0.3">
@@ -6868,6 +7000,7 @@
     </row>
     <row r="1015" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1015" s="1"/>
+      <c r="J1015" s="2"/>
       <c r="K1015" s="1"/>
     </row>
     <row r="1016" spans="8:11" x14ac:dyDescent="0.3">
@@ -6891,6 +7024,7 @@
     <row r="1019" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1019" s="2"/>
       <c r="I1019" s="1"/>
+      <c r="J1019" s="2"/>
       <c r="K1019" s="1"/>
     </row>
     <row r="1020" spans="8:11" x14ac:dyDescent="0.3">
@@ -6908,6 +7042,7 @@
     <row r="1022" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1022" s="2"/>
       <c r="I1022" s="1"/>
+      <c r="J1022" s="2"/>
       <c r="K1022" s="1"/>
     </row>
     <row r="1023" spans="8:11" x14ac:dyDescent="0.3">
@@ -6954,11 +7089,13 @@
     </row>
     <row r="1030" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1030" s="1"/>
+      <c r="J1030" s="2"/>
       <c r="K1030" s="1"/>
     </row>
     <row r="1031" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1031" s="2"/>
       <c r="I1031" s="1"/>
+      <c r="J1031" s="2"/>
       <c r="K1031" s="1"/>
     </row>
     <row r="1032" spans="8:11" x14ac:dyDescent="0.3">
@@ -7000,11 +7137,13 @@
     <row r="1038" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1038" s="2"/>
       <c r="I1038" s="1"/>
+      <c r="J1038" s="2"/>
       <c r="K1038" s="1"/>
     </row>
     <row r="1039" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1039" s="2"/>
       <c r="I1039" s="1"/>
+      <c r="J1039" s="2"/>
       <c r="K1039" s="1"/>
     </row>
     <row r="1040" spans="8:11" x14ac:dyDescent="0.3">
@@ -7022,6 +7161,7 @@
     <row r="1042" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1042" s="2"/>
       <c r="I1042" s="1"/>
+      <c r="J1042" s="2"/>
       <c r="K1042" s="1"/>
     </row>
     <row r="1043" spans="8:11" x14ac:dyDescent="0.3">
@@ -7033,6 +7173,7 @@
     <row r="1044" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1044" s="2"/>
       <c r="I1044" s="1"/>
+      <c r="J1044" s="2"/>
       <c r="K1044" s="1"/>
     </row>
     <row r="1045" spans="8:11" x14ac:dyDescent="0.3">
@@ -7044,6 +7185,7 @@
     <row r="1046" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1046" s="2"/>
       <c r="I1046" s="1"/>
+      <c r="J1046" s="2"/>
       <c r="K1046" s="1"/>
     </row>
     <row r="1047" spans="8:11" x14ac:dyDescent="0.3">
@@ -7061,6 +7203,7 @@
     <row r="1049" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1049" s="2"/>
       <c r="I1049" s="1"/>
+      <c r="J1049" s="2"/>
       <c r="K1049" s="1"/>
     </row>
     <row r="1050" spans="8:11" x14ac:dyDescent="0.3">
@@ -7138,6 +7281,7 @@
     <row r="1062" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1062" s="2"/>
       <c r="I1062" s="1"/>
+      <c r="J1062" s="2"/>
       <c r="K1062" s="1"/>
     </row>
     <row r="1063" spans="8:11" x14ac:dyDescent="0.3">
@@ -7167,6 +7311,7 @@
     <row r="1067" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1067" s="2"/>
       <c r="I1067" s="1"/>
+      <c r="J1067" s="2"/>
       <c r="K1067" s="1"/>
     </row>
     <row r="1068" spans="8:11" x14ac:dyDescent="0.3">
@@ -7178,16 +7323,19 @@
     <row r="1069" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1069" s="2"/>
       <c r="I1069" s="1"/>
+      <c r="J1069" s="2"/>
       <c r="K1069" s="1"/>
     </row>
     <row r="1070" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1070" s="2"/>
       <c r="I1070" s="1"/>
+      <c r="J1070" s="2"/>
       <c r="K1070" s="1"/>
     </row>
     <row r="1071" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1071" s="2"/>
       <c r="I1071" s="1"/>
+      <c r="J1071" s="2"/>
       <c r="K1071" s="1"/>
     </row>
     <row r="1072" spans="8:11" x14ac:dyDescent="0.3">
@@ -7199,16 +7347,19 @@
     <row r="1073" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1073" s="2"/>
       <c r="I1073" s="1"/>
+      <c r="J1073" s="2"/>
       <c r="K1073" s="1"/>
     </row>
     <row r="1074" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1074" s="2"/>
       <c r="I1074" s="1"/>
+      <c r="J1074" s="2"/>
       <c r="K1074" s="1"/>
     </row>
     <row r="1075" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1075" s="2"/>
       <c r="I1075" s="1"/>
+      <c r="J1075" s="2"/>
       <c r="K1075" s="1"/>
     </row>
     <row r="1076" spans="8:11" x14ac:dyDescent="0.3">
@@ -7220,11 +7371,13 @@
     <row r="1077" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1077" s="2"/>
       <c r="I1077" s="1"/>
+      <c r="J1077" s="2"/>
       <c r="K1077" s="1"/>
     </row>
     <row r="1078" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1078" s="2"/>
       <c r="I1078" s="1"/>
+      <c r="J1078" s="2"/>
       <c r="K1078" s="1"/>
     </row>
     <row r="1079" spans="8:11" x14ac:dyDescent="0.3">
@@ -7248,6 +7401,7 @@
     <row r="1082" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1082" s="2"/>
       <c r="I1082" s="1"/>
+      <c r="J1082" s="2"/>
       <c r="K1082" s="1"/>
     </row>
     <row r="1083" spans="8:11" x14ac:dyDescent="0.3">
@@ -7289,6 +7443,7 @@
     <row r="1089" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1089" s="2"/>
       <c r="I1089" s="1"/>
+      <c r="J1089" s="2"/>
       <c r="K1089" s="1"/>
     </row>
     <row r="1090" spans="8:11" x14ac:dyDescent="0.3">
@@ -7318,21 +7473,25 @@
     <row r="1094" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1094" s="2"/>
       <c r="I1094" s="1"/>
+      <c r="J1094" s="2"/>
       <c r="K1094" s="1"/>
     </row>
     <row r="1095" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1095" s="2"/>
       <c r="I1095" s="1"/>
+      <c r="J1095" s="2"/>
       <c r="K1095" s="1"/>
     </row>
     <row r="1096" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1096" s="2"/>
       <c r="I1096" s="1"/>
+      <c r="J1096" s="2"/>
       <c r="K1096" s="1"/>
     </row>
     <row r="1097" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1097" s="2"/>
       <c r="I1097" s="1"/>
+      <c r="J1097" s="2"/>
       <c r="K1097" s="1"/>
     </row>
     <row r="1098" spans="8:11" x14ac:dyDescent="0.3">
@@ -7344,6 +7503,7 @@
     <row r="1099" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1099" s="2"/>
       <c r="I1099" s="1"/>
+      <c r="J1099" s="2"/>
       <c r="K1099" s="1"/>
     </row>
     <row r="1100" spans="8:11" x14ac:dyDescent="0.3">
@@ -7361,6 +7521,7 @@
     <row r="1102" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1102" s="2"/>
       <c r="I1102" s="1"/>
+      <c r="J1102" s="2"/>
       <c r="K1102" s="1"/>
     </row>
     <row r="1103" spans="8:11" x14ac:dyDescent="0.3">
@@ -7400,11 +7561,13 @@
     <row r="1109" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1109" s="2"/>
       <c r="I1109" s="1"/>
+      <c r="J1109" s="2"/>
       <c r="K1109" s="1"/>
     </row>
     <row r="1110" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1110" s="2"/>
       <c r="I1110" s="1"/>
+      <c r="J1110" s="2"/>
       <c r="K1110" s="1"/>
     </row>
     <row r="1111" spans="8:11" x14ac:dyDescent="0.3">
@@ -7452,6 +7615,7 @@
     <row r="1118" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1118" s="2"/>
       <c r="I1118" s="1"/>
+      <c r="J1118" s="2"/>
       <c r="K1118" s="1"/>
     </row>
     <row r="1119" spans="8:11" x14ac:dyDescent="0.3">
@@ -7481,6 +7645,7 @@
     <row r="1123" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1123" s="2"/>
       <c r="I1123" s="1"/>
+      <c r="J1123" s="2"/>
       <c r="K1123" s="1"/>
     </row>
     <row r="1124" spans="8:11" x14ac:dyDescent="0.3">
@@ -7557,6 +7722,7 @@
     <row r="1136" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1136" s="2"/>
       <c r="I1136" s="1"/>
+      <c r="J1136" s="2"/>
       <c r="K1136" s="1"/>
     </row>
     <row r="1137" spans="8:11" x14ac:dyDescent="0.3">
@@ -7603,6 +7769,7 @@
     <row r="1144" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1144" s="2"/>
       <c r="I1144" s="1"/>
+      <c r="J1144" s="2"/>
       <c r="K1144" s="1"/>
     </row>
     <row r="1145" spans="8:11" x14ac:dyDescent="0.3">
@@ -7638,11 +7805,13 @@
     <row r="1150" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1150" s="2"/>
       <c r="I1150" s="1"/>
+      <c r="J1150" s="2"/>
       <c r="K1150" s="1"/>
     </row>
     <row r="1151" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1151" s="2"/>
       <c r="I1151" s="1"/>
+      <c r="J1151" s="2"/>
       <c r="K1151" s="1"/>
     </row>
     <row r="1152" spans="8:11" x14ac:dyDescent="0.3">
@@ -7659,6 +7828,7 @@
     <row r="1154" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1154" s="2"/>
       <c r="I1154" s="1"/>
+      <c r="J1154" s="2"/>
       <c r="K1154" s="1"/>
     </row>
     <row r="1155" spans="8:11" x14ac:dyDescent="0.3">
@@ -7669,6 +7839,7 @@
     <row r="1156" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1156" s="2"/>
       <c r="I1156" s="1"/>
+      <c r="J1156" s="2"/>
       <c r="K1156" s="1"/>
     </row>
     <row r="1157" spans="8:11" x14ac:dyDescent="0.3">
@@ -7704,6 +7875,7 @@
     <row r="1162" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1162" s="2"/>
       <c r="I1162" s="1"/>
+      <c r="J1162" s="2"/>
       <c r="K1162" s="1"/>
     </row>
     <row r="1163" spans="8:11" x14ac:dyDescent="0.3">
@@ -7715,6 +7887,7 @@
     <row r="1164" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1164" s="2"/>
       <c r="I1164" s="1"/>
+      <c r="J1164" s="2"/>
       <c r="K1164" s="1"/>
     </row>
     <row r="1165" spans="8:11" x14ac:dyDescent="0.3">
@@ -7726,6 +7899,7 @@
     <row r="1166" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1166" s="2"/>
       <c r="I1166" s="1"/>
+      <c r="J1166" s="2"/>
       <c r="K1166" s="1"/>
     </row>
     <row r="1167" spans="8:11" x14ac:dyDescent="0.3">
@@ -7737,6 +7911,7 @@
     <row r="1168" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1168" s="2"/>
       <c r="I1168" s="1"/>
+      <c r="J1168" s="2"/>
       <c r="K1168" s="1"/>
     </row>
     <row r="1169" spans="8:11" x14ac:dyDescent="0.3">
@@ -7748,6 +7923,7 @@
     <row r="1170" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1170" s="2"/>
       <c r="I1170" s="1"/>
+      <c r="J1170" s="2"/>
       <c r="K1170" s="1"/>
     </row>
     <row r="1171" spans="8:11" x14ac:dyDescent="0.3">
@@ -7789,6 +7965,7 @@
     <row r="1177" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1177" s="2"/>
       <c r="I1177" s="1"/>
+      <c r="J1177" s="2"/>
       <c r="K1177" s="1"/>
     </row>
     <row r="1178" spans="8:11" x14ac:dyDescent="0.3">
@@ -7806,6 +7983,7 @@
     <row r="1180" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1180" s="2"/>
       <c r="I1180" s="1"/>
+      <c r="J1180" s="2"/>
       <c r="K1180" s="1"/>
     </row>
     <row r="1181" spans="8:11" x14ac:dyDescent="0.3">
@@ -7823,6 +8001,7 @@
     <row r="1183" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1183" s="2"/>
       <c r="I1183" s="1"/>
+      <c r="J1183" s="2"/>
       <c r="K1183" s="1"/>
     </row>
     <row r="1184" spans="8:11" x14ac:dyDescent="0.3">
@@ -7864,6 +8043,7 @@
     <row r="1190" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1190" s="2"/>
       <c r="I1190" s="1"/>
+      <c r="J1190" s="2"/>
       <c r="K1190" s="1"/>
     </row>
     <row r="1191" spans="8:11" x14ac:dyDescent="0.3">
@@ -7887,6 +8067,7 @@
     <row r="1194" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1194" s="2"/>
       <c r="I1194" s="1"/>
+      <c r="J1194" s="2"/>
       <c r="K1194" s="1"/>
     </row>
     <row r="1195" spans="8:11" x14ac:dyDescent="0.3">
@@ -7933,6 +8114,7 @@
     <row r="1202" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1202" s="2"/>
       <c r="I1202" s="1"/>
+      <c r="J1202" s="2"/>
       <c r="K1202" s="1"/>
     </row>
     <row r="1203" spans="8:11" x14ac:dyDescent="0.3">
@@ -7968,6 +8150,7 @@
     <row r="1208" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1208" s="2"/>
       <c r="I1208" s="1"/>
+      <c r="J1208" s="2"/>
       <c r="K1208" s="1"/>
     </row>
     <row r="1209" spans="8:11" x14ac:dyDescent="0.3">
@@ -7991,6 +8174,7 @@
     <row r="1212" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1212" s="2"/>
       <c r="I1212" s="1"/>
+      <c r="J1212" s="2"/>
       <c r="K1212" s="1"/>
     </row>
     <row r="1213" spans="8:11" x14ac:dyDescent="0.3">
@@ -8031,6 +8215,7 @@
     <row r="1219" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1219" s="2"/>
       <c r="I1219" s="1"/>
+      <c r="J1219" s="2"/>
       <c r="K1219" s="1"/>
     </row>
     <row r="1220" spans="8:11" x14ac:dyDescent="0.3">
@@ -8048,11 +8233,13 @@
     <row r="1222" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1222" s="2"/>
       <c r="I1222" s="1"/>
+      <c r="J1222" s="2"/>
       <c r="K1222" s="1"/>
     </row>
     <row r="1223" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1223" s="2"/>
       <c r="I1223" s="1"/>
+      <c r="J1223" s="2"/>
       <c r="K1223" s="1"/>
     </row>
     <row r="1224" spans="8:11" x14ac:dyDescent="0.3">
@@ -8111,6 +8298,7 @@
     <row r="1233" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1233" s="2"/>
       <c r="I1233" s="1"/>
+      <c r="J1233" s="2"/>
       <c r="K1233" s="1"/>
     </row>
     <row r="1234" spans="8:11" x14ac:dyDescent="0.3">
@@ -8127,6 +8315,7 @@
     <row r="1236" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1236" s="2"/>
       <c r="I1236" s="1"/>
+      <c r="J1236" s="2"/>
       <c r="K1236" s="1"/>
     </row>
     <row r="1237" spans="8:11" x14ac:dyDescent="0.3">
@@ -8138,6 +8327,7 @@
     <row r="1238" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1238" s="2"/>
       <c r="I1238" s="1"/>
+      <c r="J1238" s="2"/>
       <c r="K1238" s="1"/>
     </row>
     <row r="1239" spans="8:11" x14ac:dyDescent="0.3">
@@ -8149,11 +8339,13 @@
     <row r="1240" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1240" s="2"/>
       <c r="I1240" s="1"/>
+      <c r="J1240" s="2"/>
       <c r="K1240" s="1"/>
     </row>
     <row r="1241" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1241" s="2"/>
       <c r="I1241" s="1"/>
+      <c r="J1241" s="2"/>
       <c r="K1241" s="1"/>
     </row>
     <row r="1242" spans="8:11" x14ac:dyDescent="0.3">
@@ -8189,6 +8381,7 @@
     <row r="1247" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1247" s="2"/>
       <c r="I1247" s="1"/>
+      <c r="J1247" s="2"/>
       <c r="K1247" s="1"/>
     </row>
     <row r="1248" spans="8:11" x14ac:dyDescent="0.3">
@@ -8241,6 +8434,7 @@
     <row r="1256" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1256" s="2"/>
       <c r="I1256" s="1"/>
+      <c r="J1256" s="2"/>
       <c r="K1256" s="1"/>
     </row>
     <row r="1257" spans="8:11" x14ac:dyDescent="0.3">
@@ -8251,6 +8445,7 @@
     </row>
     <row r="1258" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1258" s="1"/>
+      <c r="J1258" s="2"/>
       <c r="K1258" s="1"/>
     </row>
     <row r="1259" spans="8:11" x14ac:dyDescent="0.3">
@@ -8266,6 +8461,7 @@
     </row>
     <row r="1261" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1261" s="1"/>
+      <c r="J1261" s="2"/>
       <c r="K1261" s="1"/>
     </row>
     <row r="1262" spans="8:11" x14ac:dyDescent="0.3">
@@ -8289,16 +8485,19 @@
     <row r="1265" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1265" s="2"/>
       <c r="I1265" s="1"/>
+      <c r="J1265" s="2"/>
       <c r="K1265" s="1"/>
     </row>
     <row r="1266" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1266" s="2"/>
       <c r="I1266" s="1"/>
+      <c r="J1266" s="2"/>
       <c r="K1266" s="1"/>
     </row>
     <row r="1267" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1267" s="2"/>
       <c r="I1267" s="1"/>
+      <c r="J1267" s="2"/>
       <c r="K1267" s="1"/>
     </row>
     <row r="1268" spans="8:11" x14ac:dyDescent="0.3">
@@ -8369,6 +8568,7 @@
     <row r="1279" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1279" s="2"/>
       <c r="I1279" s="1"/>
+      <c r="J1279" s="2"/>
       <c r="K1279" s="1"/>
     </row>
     <row r="1280" spans="8:11" x14ac:dyDescent="0.3">
@@ -8380,6 +8580,7 @@
     <row r="1281" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1281" s="2"/>
       <c r="I1281" s="1"/>
+      <c r="J1281" s="2"/>
       <c r="K1281" s="1"/>
     </row>
     <row r="1282" spans="8:11" x14ac:dyDescent="0.3">
@@ -8480,6 +8681,8 @@
     <row r="1298" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1298" s="2"/>
       <c r="I1298" s="1"/>
+      <c r="J1298" s="2"/>
+      <c r="K1298" s="1"/>
     </row>
     <row r="1299" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1299" s="2"/>
@@ -8536,6 +8739,7 @@
     <row r="1308" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1308" s="2"/>
       <c r="I1308" s="1"/>
+      <c r="J1308" s="2"/>
       <c r="K1308" s="1"/>
     </row>
     <row r="1309" spans="8:11" x14ac:dyDescent="0.3">
@@ -8559,6 +8763,7 @@
     <row r="1312" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1312" s="2"/>
       <c r="I1312" s="1"/>
+      <c r="J1312" s="2"/>
       <c r="K1312" s="1"/>
     </row>
     <row r="1313" spans="8:11" x14ac:dyDescent="0.3">
@@ -8683,6 +8888,7 @@
     <row r="1333" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1333" s="2"/>
       <c r="I1333" s="1"/>
+      <c r="J1333" s="2"/>
       <c r="K1333" s="1"/>
     </row>
     <row r="1334" spans="8:11" x14ac:dyDescent="0.3">
@@ -8841,6 +9047,7 @@
     <row r="1360" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1360" s="2"/>
       <c r="I1360" s="1"/>
+      <c r="J1360" s="2"/>
       <c r="K1360" s="1"/>
     </row>
     <row r="1361" spans="8:11" x14ac:dyDescent="0.3">
@@ -8858,6 +9065,7 @@
     <row r="1363" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1363" s="2"/>
       <c r="I1363" s="1"/>
+      <c r="J1363" s="2"/>
       <c r="K1363" s="1"/>
     </row>
     <row r="1364" spans="8:11" x14ac:dyDescent="0.3">
@@ -8898,6 +9106,7 @@
     <row r="1370" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1370" s="2"/>
       <c r="I1370" s="1"/>
+      <c r="J1370" s="2"/>
       <c r="K1370" s="1"/>
     </row>
     <row r="1371" spans="8:11" x14ac:dyDescent="0.3">
@@ -9230,6 +9439,7 @@
     <row r="1427" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1427" s="2"/>
       <c r="I1427" s="1"/>
+      <c r="J1427" s="2"/>
       <c r="K1427" s="1"/>
     </row>
     <row r="1428" spans="8:11" x14ac:dyDescent="0.3">
@@ -9318,6 +9528,7 @@
     <row r="1442" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1442" s="2"/>
       <c r="I1442" s="1"/>
+      <c r="J1442" s="2"/>
       <c r="K1442" s="1"/>
     </row>
     <row r="1443" spans="8:11" x14ac:dyDescent="0.3">
@@ -9411,6 +9622,7 @@
     <row r="1458" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1458" s="2"/>
       <c r="I1458" s="1"/>
+      <c r="J1458" s="2"/>
       <c r="K1458" s="1"/>
     </row>
     <row r="1459" spans="8:11" x14ac:dyDescent="0.3">
@@ -9470,11 +9682,13 @@
     <row r="1468" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1468" s="2"/>
       <c r="I1468" s="1"/>
+      <c r="J1468" s="2"/>
       <c r="K1468" s="1"/>
     </row>
     <row r="1469" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1469" s="2"/>
       <c r="I1469" s="1"/>
+      <c r="J1469" s="2"/>
       <c r="K1469" s="1"/>
     </row>
     <row r="1470" spans="8:11" x14ac:dyDescent="0.3">
@@ -9526,6 +9740,7 @@
     </row>
     <row r="1478" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1478" s="1"/>
+      <c r="J1478" s="2"/>
       <c r="K1478" s="1"/>
     </row>
     <row r="1479" spans="8:11" x14ac:dyDescent="0.3">
@@ -9567,6 +9782,7 @@
     <row r="1485" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1485" s="2"/>
       <c r="I1485" s="1"/>
+      <c r="J1485" s="2"/>
       <c r="K1485" s="1"/>
     </row>
     <row r="1486" spans="8:11" x14ac:dyDescent="0.3">
@@ -9611,6 +9827,7 @@
     </row>
     <row r="1493" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1493" s="1"/>
+      <c r="J1493" s="2"/>
       <c r="K1493" s="1"/>
     </row>
     <row r="1494" spans="8:11" x14ac:dyDescent="0.3">
@@ -9657,11 +9874,13 @@
     <row r="1501" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1501" s="2"/>
       <c r="I1501" s="1"/>
+      <c r="J1501" s="2"/>
       <c r="K1501" s="1"/>
     </row>
     <row r="1502" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1502" s="2"/>
       <c r="I1502" s="1"/>
+      <c r="J1502" s="2"/>
       <c r="K1502" s="1"/>
     </row>
     <row r="1503" spans="8:11" x14ac:dyDescent="0.3">
@@ -9859,6 +10078,7 @@
     <row r="1535" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1535" s="2"/>
       <c r="I1535" s="1"/>
+      <c r="J1535" s="2"/>
       <c r="K1535" s="1"/>
     </row>
     <row r="1536" spans="8:11" x14ac:dyDescent="0.3">
@@ -9888,6 +10108,8 @@
     <row r="1540" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1540" s="2"/>
       <c r="I1540" s="1"/>
+      <c r="J1540" s="2"/>
+      <c r="K1540" s="1"/>
     </row>
     <row r="1541" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1541" s="1"/>
@@ -9903,6 +10125,7 @@
     <row r="1543" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1543" s="2"/>
       <c r="I1543" s="1"/>
+      <c r="J1543" s="2"/>
       <c r="K1543" s="1"/>
     </row>
     <row r="1544" spans="8:11" x14ac:dyDescent="0.3">
@@ -9962,6 +10185,7 @@
     <row r="1553" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1553" s="2"/>
       <c r="I1553" s="1"/>
+      <c r="J1553" s="2"/>
       <c r="K1553" s="1"/>
     </row>
     <row r="1554" spans="8:11" x14ac:dyDescent="0.3">
@@ -10033,6 +10257,7 @@
     <row r="1565" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1565" s="2"/>
       <c r="I1565" s="1"/>
+      <c r="J1565" s="2"/>
       <c r="K1565" s="1"/>
     </row>
     <row r="1566" spans="8:11" x14ac:dyDescent="0.3">
@@ -10074,6 +10299,7 @@
     <row r="1572" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1572" s="2"/>
       <c r="I1572" s="1"/>
+      <c r="J1572" s="2"/>
       <c r="K1572" s="1"/>
     </row>
     <row r="1573" spans="8:11" x14ac:dyDescent="0.3">
@@ -10192,6 +10418,7 @@
     <row r="1592" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1592" s="2"/>
       <c r="I1592" s="1"/>
+      <c r="J1592" s="2"/>
       <c r="K1592" s="1"/>
     </row>
     <row r="1593" spans="8:11" x14ac:dyDescent="0.3">
@@ -10256,6 +10483,7 @@
     <row r="1603" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1603" s="2"/>
       <c r="I1603" s="1"/>
+      <c r="J1603" s="2"/>
       <c r="K1603" s="1"/>
     </row>
     <row r="1604" spans="8:11" x14ac:dyDescent="0.3">
@@ -10380,6 +10608,7 @@
     <row r="1624" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1624" s="2"/>
       <c r="I1624" s="1"/>
+      <c r="J1624" s="2"/>
       <c r="K1624" s="1"/>
     </row>
     <row r="1625" spans="8:11" x14ac:dyDescent="0.3">
@@ -10606,6 +10835,7 @@
     <row r="1662" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1662" s="2"/>
       <c r="I1662" s="1"/>
+      <c r="J1662" s="2"/>
       <c r="K1662" s="1"/>
     </row>
     <row r="1663" spans="8:11" x14ac:dyDescent="0.3">
@@ -10723,6 +10953,7 @@
     <row r="1682" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1682" s="2"/>
       <c r="I1682" s="1"/>
+      <c r="J1682" s="2"/>
       <c r="K1682" s="1"/>
     </row>
     <row r="1683" spans="8:11" x14ac:dyDescent="0.3">
@@ -10806,6 +11037,7 @@
     <row r="1696" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1696" s="2"/>
       <c r="I1696" s="1"/>
+      <c r="J1696" s="2"/>
       <c r="K1696" s="1"/>
     </row>
     <row r="1697" spans="8:11" x14ac:dyDescent="0.3">
@@ -10865,6 +11097,7 @@
     <row r="1706" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1706" s="2"/>
       <c r="I1706" s="1"/>
+      <c r="J1706" s="2"/>
       <c r="K1706" s="1"/>
     </row>
     <row r="1707" spans="8:11" x14ac:dyDescent="0.3">
@@ -10888,6 +11121,7 @@
     <row r="1710" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1710" s="2"/>
       <c r="I1710" s="1"/>
+      <c r="J1710" s="2"/>
       <c r="K1710" s="1"/>
     </row>
     <row r="1711" spans="8:11" x14ac:dyDescent="0.3">
@@ -10935,6 +11169,7 @@
     <row r="1718" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1718" s="2"/>
       <c r="I1718" s="1"/>
+      <c r="J1718" s="2"/>
       <c r="K1718" s="1"/>
     </row>
     <row r="1719" spans="8:11" x14ac:dyDescent="0.3">
@@ -10994,6 +11229,7 @@
     <row r="1728" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1728" s="2"/>
       <c r="I1728" s="1"/>
+      <c r="J1728" s="2"/>
       <c r="K1728" s="1"/>
     </row>
     <row r="1729" spans="8:11" x14ac:dyDescent="0.3">
@@ -11017,6 +11253,7 @@
     <row r="1732" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1732" s="2"/>
       <c r="I1732" s="1"/>
+      <c r="J1732" s="2"/>
       <c r="K1732" s="1"/>
     </row>
     <row r="1733" spans="8:11" x14ac:dyDescent="0.3">
@@ -11034,6 +11271,7 @@
     <row r="1735" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1735" s="2"/>
       <c r="I1735" s="1"/>
+      <c r="J1735" s="2"/>
       <c r="K1735" s="1"/>
     </row>
     <row r="1736" spans="8:11" x14ac:dyDescent="0.3">
@@ -11117,6 +11355,7 @@
     <row r="1749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1749" s="2"/>
       <c r="I1749" s="1"/>
+      <c r="J1749" s="2"/>
       <c r="K1749" s="1"/>
     </row>
     <row r="1750" spans="8:11" x14ac:dyDescent="0.3">
@@ -11308,6 +11547,7 @@
     <row r="1781" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1781" s="2"/>
       <c r="I1781" s="1"/>
+      <c r="J1781" s="2"/>
       <c r="K1781" s="1"/>
     </row>
     <row r="1782" spans="8:11" x14ac:dyDescent="0.3">
@@ -39164,6 +39404,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -39171,6 +39412,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -39178,6 +39420,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -39193,6 +39436,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -39202,6 +39446,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -39209,9 +39454,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -39219,12 +39470,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -39232,12 +39486,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -39249,9 +39506,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -39266,6 +39525,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -39292,6 +39552,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -39302,7 +39563,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -39310,6 +39576,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -39321,6 +39588,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -39328,6 +39596,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -39342,13 +39611,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -39359,15 +39634,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -39383,6 +39661,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -39401,6 +39680,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -39412,6 +39692,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -39429,18 +39710,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -39469,6 +39755,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -39476,9 +39763,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -39501,12 +39790,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -39521,9 +39813,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -39539,12 +39833,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -39565,6 +39861,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -39576,9 +39873,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -39590,6 +39889,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -39629,9 +39929,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -39639,9 +39941,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -39652,6 +39956,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -39659,18 +39964,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -39678,6 +39991,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -39688,6 +40002,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -39714,15 +40029,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -39744,6 +40063,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -39751,9 +40071,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -39761,6 +40083,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -39772,6 +40095,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -39786,6 +40110,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -39795,6 +40123,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -39806,6 +40135,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -39816,10 +40146,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -39827,6 +40162,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -39841,6 +40177,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -39863,6 +40200,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -39882,25 +40220,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -39908,6 +40258,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -39915,15 +40266,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -39937,6 +40295,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -39955,9 +40314,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -39965,9 +40326,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -39975,6 +40338,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -39991,10 +40355,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
